--- a/Escenarios/Ejemplo_Casos de prueba.xlsx
+++ b/Escenarios/Ejemplo_Casos de prueba.xlsx
@@ -468,7 +468,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -728,6 +728,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1720,7 +1723,7 @@
       </c>
       <c r="J3" s="44" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K3" s="36" t="inlineStr">
@@ -1728,9 +1731,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L3" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L3" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M3" s="44" t="n"/>
@@ -1807,7 +1810,7 @@
       </c>
       <c r="J4" s="51" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K4" s="36" t="inlineStr">
@@ -1815,9 +1818,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L4" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L4" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M4" s="27" t="n"/>
@@ -1893,7 +1896,7 @@
       </c>
       <c r="J5" s="44" t="inlineStr">
         <is>
-          <t>TimeoutException al buscar mensaje error</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K5" s="36" t="inlineStr">
@@ -1980,7 +1983,7 @@
       </c>
       <c r="J6" s="44" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K6" s="36" t="inlineStr">
@@ -1988,9 +1991,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L6" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L6" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M6" s="44" t="n"/>
@@ -2067,7 +2070,7 @@
       </c>
       <c r="J7" s="44" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K7" s="36" t="inlineStr">
@@ -2075,9 +2078,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L7" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L7" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M7" s="44" t="n"/>
@@ -2153,7 +2156,7 @@
       </c>
       <c r="J8" s="44" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K8" s="36" t="inlineStr">
@@ -2161,9 +2164,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L8" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L8" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M8" s="44" t="n"/>
@@ -2240,7 +2243,7 @@
       </c>
       <c r="J9" s="48" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K9" s="36" t="inlineStr">
@@ -2248,9 +2251,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L9" s="92" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L9" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M9" s="48" t="n"/>
@@ -2326,7 +2329,7 @@
       </c>
       <c r="J10" s="48" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K10" s="36" t="inlineStr">
@@ -2334,9 +2337,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L10" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M10" s="48" t="n"/>
@@ -2413,7 +2416,7 @@
       </c>
       <c r="J11" s="44" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K11" s="36" t="inlineStr">
@@ -2421,9 +2424,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L11" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L11" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M11" s="44" t="n"/>
@@ -2500,7 +2503,7 @@
       </c>
       <c r="J12" s="47" t="inlineStr">
         <is>
-          <t>Fallo en el resultado: AssertionError</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K12" s="36" t="inlineStr">
@@ -2586,7 +2589,7 @@
       </c>
       <c r="J13" s="47" t="inlineStr">
         <is>
-          <t>Escenario automatizado ejecutado correctamente.</t>
+          <t>Escenario falló. Ver reporte HTML.</t>
         </is>
       </c>
       <c r="K13" s="36" t="inlineStr">
@@ -2594,9 +2597,9 @@
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L13" s="90" t="inlineStr">
-        <is>
-          <t>Pasó</t>
+      <c r="L13" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
         </is>
       </c>
       <c r="M13" s="27" t="n"/>
@@ -7428,13 +7431,21 @@
           <t>Se muestra un mensaje de campo requerido y no hay confirmación de éxito.</t>
         </is>
       </c>
-      <c r="J69" s="27" t="n"/>
+      <c r="J69" s="27" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K69" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L69" s="27" t="n"/>
+      <c r="L69" s="91" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M69" s="27" t="n"/>
       <c r="N69" s="27" t="n"/>
       <c r="O69" s="80" t="inlineStr">
@@ -7508,13 +7519,21 @@
           <t>Un elemento de confirmación es visible en el DOM.</t>
         </is>
       </c>
-      <c r="J70" s="28" t="n"/>
+      <c r="J70" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K70" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L70" s="28" t="n"/>
+      <c r="L70" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M70" s="28" t="n"/>
       <c r="N70" s="28" t="n"/>
       <c r="O70" s="83" t="inlineStr">
@@ -7586,13 +7605,21 @@
           <t>No se crea ningún evento nuevo ni aparece marcador en la fecha.</t>
         </is>
       </c>
-      <c r="J71" s="28" t="n"/>
+      <c r="J71" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K71" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L71" s="28" t="n"/>
+      <c r="L71" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M71" s="28" t="n"/>
       <c r="N71" s="28" t="n"/>
       <c r="O71" s="80" t="inlineStr">
@@ -7667,13 +7694,21 @@
           <t>El calendario muestra el evento creado y su detalle contiene la información ingresada.</t>
         </is>
       </c>
-      <c r="J72" s="28" t="n"/>
+      <c r="J72" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K72" s="36" t="inlineStr">
         <is>
           <t>Ruta Critica</t>
         </is>
       </c>
-      <c r="L72" s="28" t="n"/>
+      <c r="L72" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M72" s="28" t="n"/>
       <c r="N72" s="28" t="n"/>
       <c r="O72" s="80" t="inlineStr">
@@ -7747,13 +7782,21 @@
           <t>La ciudad inválida no se guarda y reloj/clima mantienen la configuración anterior.</t>
         </is>
       </c>
-      <c r="J73" s="28" t="n"/>
+      <c r="J73" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K73" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L73" s="28" t="n"/>
+      <c r="L73" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M73" s="28" t="n"/>
       <c r="N73" s="28" t="n"/>
       <c r="O73" s="80" t="inlineStr">
@@ -7829,13 +7872,21 @@
           <t>La ciudad configurada en preferencias se refleja en reloj y clima.</t>
         </is>
       </c>
-      <c r="J74" s="28" t="n"/>
+      <c r="J74" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K74" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L74" s="28" t="n"/>
+      <c r="L74" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M74" s="28" t="n"/>
       <c r="N74" s="28" t="n"/>
       <c r="O74" s="80" t="inlineStr">
@@ -7908,13 +7959,21 @@
           <t>No aparece confirmación de pago y el sistema vuelve al estado previo.</t>
         </is>
       </c>
-      <c r="J75" s="28" t="n"/>
+      <c r="J75" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K75" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L75" s="28" t="n"/>
+      <c r="L75" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M75" s="28" t="n"/>
       <c r="N75" s="28" t="n"/>
       <c r="O75" s="80" t="inlineStr">
@@ -7988,13 +8047,21 @@
           <t>Se muestra confirmación exitosa en el DOM.</t>
         </is>
       </c>
-      <c r="J76" s="28" t="n"/>
+      <c r="J76" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K76" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L76" s="28" t="n"/>
+      <c r="L76" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M76" s="28" t="n"/>
       <c r="N76" s="28" t="n"/>
       <c r="O76" s="80" t="inlineStr">
@@ -8069,13 +8136,21 @@
           <t>La hora del reloj mundial de Tokyo es coherente con el conversor, con diferencia máxima de 1 minuto.</t>
         </is>
       </c>
-      <c r="J77" s="28" t="n"/>
+      <c r="J77" s="28" t="inlineStr">
+        <is>
+          <t>Fallo en 'la hora mostrada en el reloj mundial para Tokio coincide con la conversión previa con un margen máximo de 1 minuto': Conversión=18 vs reloj=8</t>
+        </is>
+      </c>
       <c r="K77" s="36" t="inlineStr">
         <is>
           <t>Ruta Crítica</t>
         </is>
       </c>
-      <c r="L77" s="28" t="n"/>
+      <c r="L77" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M77" s="28" t="n"/>
       <c r="N77" s="28" t="n"/>
       <c r="O77" s="80" t="inlineStr">
@@ -8150,13 +8225,21 @@
           <t>El temporizador inicia correctamente y la calculadora devuelve 30 días.</t>
         </is>
       </c>
-      <c r="J78" s="28" t="n"/>
+      <c r="J78" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K78" s="36" t="inlineStr">
         <is>
           <t>Ruta Crítica</t>
         </is>
       </c>
-      <c r="L78" s="28" t="n"/>
+      <c r="L78" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M78" s="28" t="n"/>
       <c r="N78" s="28" t="n"/>
       <c r="O78" s="80" t="inlineStr">
@@ -8229,13 +8312,21 @@
           <t>Se muestran datos de clima y astronomía no vacíos para Bogotá.</t>
         </is>
       </c>
-      <c r="J79" s="28" t="n"/>
+      <c r="J79" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K79" s="36" t="inlineStr">
         <is>
           <t>Ruta Crítica</t>
         </is>
       </c>
-      <c r="L79" s="28" t="n"/>
+      <c r="L79" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M79" s="28" t="n"/>
       <c r="N79" s="28" t="n"/>
       <c r="O79" s="80" t="inlineStr">
@@ -8308,13 +8399,21 @@
           <t>Se muestra un mensaje de error y no se permite el acceso al perfil.</t>
         </is>
       </c>
-      <c r="J80" s="28" t="n"/>
+      <c r="J80" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K80" s="36" t="inlineStr">
         <is>
           <t>Ruta Alterna</t>
         </is>
       </c>
-      <c r="L80" s="28" t="n"/>
+      <c r="L80" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M80" s="28" t="n"/>
       <c r="N80" s="28" t="n"/>
       <c r="O80" s="80" t="inlineStr">
@@ -8391,13 +8490,21 @@
           <t>El usuario inicia sesión correctamente y las preferencias se guardan y reflejan en la interfaz.</t>
         </is>
       </c>
-      <c r="J81" s="28" t="n"/>
+      <c r="J81" s="28" t="inlineStr">
+        <is>
+          <t>Escenario falló. Ver reporte HTML.</t>
+        </is>
+      </c>
       <c r="K81" s="36" t="inlineStr">
         <is>
           <t>Ruta Critica</t>
         </is>
       </c>
-      <c r="L81" s="28" t="n"/>
+      <c r="L81" s="93" t="inlineStr">
+        <is>
+          <t>Falló</t>
+        </is>
+      </c>
       <c r="M81" s="28" t="n"/>
       <c r="N81" s="28" t="n"/>
       <c r="O81" s="80" t="inlineStr">
